--- a/assets/xlsx/월별투자수익_2026-06-01_2026-08-27.xlsx
+++ b/assets/xlsx/월별투자수익_2026-06-01_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>873940919</v>
+        <v>786782391</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>873465485</v>
+        <v>786493494</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>475434</v>
+        <v>288897</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.76</v>
+        <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0439</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>897858596</v>
+        <v>807736429</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>897352825</v>
+        <v>807419143</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>505771</v>
+        <v>317286</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.73</v>
+        <v>3.01</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>781086860</v>
+        <v>702981435</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>780652554</v>
+        <v>702712201</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>434306</v>
+        <v>269234</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.74</v>
+        <v>3.03</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.074</v>
+        <v>0.0462</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2552886375</v>
+        <v>2297500255</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2551470864</v>
+        <v>2296624838</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>1415511</v>
+        <v>875417</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2.74</v>
+        <v>3.03</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0738</v>
+        <v>0.0459</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/월별투자수익_2026-06-01_2026-08-27.xlsx
+++ b/assets/xlsx/월별투자수익_2026-06-01_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>786782422</v>
+        <v>787359606</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>786493494</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>288897</v>
+        <v>866081</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0438</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>807736457</v>
+        <v>808308293</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>807419143</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>317286</v>
+        <v>889122</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3.01</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0476</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>702981504</v>
+        <v>703486091</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>702712201</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>269234</v>
+        <v>773821</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.03</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2297500383</v>
+        <v>2299153990</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>2296624838</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>875417</v>
+        <v>2529024</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>3.03</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.1325</v>
       </c>
     </row>
   </sheetData>
